--- a/artfynd/A 54374-2025 artfynd.xlsx
+++ b/artfynd/A 54374-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94934909</v>
+        <v>111910403</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågbäcken O, Jmt</t>
+          <t>Sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408262.3821235396</v>
+        <v>408251</v>
       </c>
       <c r="R2" t="n">
-        <v>7019614.208399619</v>
+        <v>7019793</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,34 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94934875</v>
+        <v>94934075</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408361.1689940271</v>
+        <v>408682</v>
       </c>
       <c r="R3" t="n">
-        <v>7019712.202683104</v>
+        <v>7019749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +847,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94934843</v>
+        <v>94934202</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408359.8277234312</v>
+        <v>408799</v>
       </c>
       <c r="R4" t="n">
-        <v>7019744.194027731</v>
+        <v>7019920</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +948,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94934959</v>
+        <v>94934459</v>
       </c>
       <c r="B5" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,31 +989,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408498.9207677075</v>
+        <v>408848</v>
       </c>
       <c r="R5" t="n">
-        <v>7019881.091427973</v>
+        <v>7020051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,19 +1049,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grankvist och sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,6 +1065,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1144,47 +1084,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94934808</v>
+        <v>94934567</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408360.0793178566</v>
+        <v>408892</v>
       </c>
       <c r="R6" t="n">
-        <v>7019800.441558355</v>
+        <v>7020112</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,19 +1155,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,43 +1185,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94934616</v>
+        <v>94934843</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408319.3829742335</v>
+        <v>408360</v>
       </c>
       <c r="R7" t="n">
-        <v>7019700.792858806</v>
+        <v>7019744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,19 +1256,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94934160</v>
+        <v>94934875</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,27 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408760.3137404274</v>
+        <v>408361</v>
       </c>
       <c r="R8" t="n">
-        <v>7019850.259950343</v>
+        <v>7019712</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,32 +1357,18 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1503,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94934075</v>
+        <v>94934512</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408681.7170334483</v>
+        <v>408842</v>
       </c>
       <c r="R9" t="n">
-        <v>7019748.534765164</v>
+        <v>7020042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,19 +1458,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,12 +1491,7 @@
         <v>94934559</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408892.109164839</v>
+        <v>408892</v>
       </c>
       <c r="R10" t="n">
-        <v>7020112.024009729</v>
+        <v>7020112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,19 +1559,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,15 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94934202</v>
+        <v>94934160</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,26 +1600,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1778,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408799.2391855348</v>
+        <v>408760</v>
       </c>
       <c r="R11" t="n">
-        <v>7019919.808121556</v>
+        <v>7019850</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,19 +1661,14 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,7 +1677,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1851,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94934567</v>
+        <v>111910567</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,37 +1706,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sågbäcken O, Jmt</t>
+          <t>Sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408892.109164839</v>
+        <v>408284</v>
       </c>
       <c r="R12" t="n">
-        <v>7020112.024009729</v>
+        <v>7019857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,22 +1765,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,61 +1784,64 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94934459</v>
+        <v>94934959</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2010,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408847.5770301935</v>
+        <v>408499</v>
       </c>
       <c r="R13" t="n">
-        <v>7020051.188038221</v>
+        <v>7019881</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,33 +1882,17 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På grankvist och sälg.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2088,42 +1911,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94934512</v>
+        <v>94934616</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2131,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408841.9190464077</v>
+        <v>408319</v>
       </c>
       <c r="R14" t="n">
-        <v>7020042.348603209</v>
+        <v>7019701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,19 +1983,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,6 +2010,214 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94934808</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sågbäcken O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>408360</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7019800</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94934909</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sågbäcken O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>408262</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7019614</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-07-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54374-2025 artfynd.xlsx
+++ b/artfynd/A 54374-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910403</t>
         </is>
       </c>
     </row>
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934202</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934459</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934875</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934559</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934160</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111910567</t>
         </is>
       </c>
     </row>
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934959</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934616</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934808</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,8 +2293,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94934909</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>